--- a/artfynd/A 5095-2024 artfynd.xlsx
+++ b/artfynd/A 5095-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115258601</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115259553</v>
+        <v>115259071</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>349274</v>
+        <v>349246</v>
       </c>
       <c r="R3" t="n">
-        <v>6538144</v>
+        <v>6538084</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -917,7 +907,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk till frisk-fuktig mark.</t>
+          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Vid fyndplatsen rinner en mindre bäck och inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk till frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115262749</v>
+        <v>115259553</v>
       </c>
       <c r="B4" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>349279</v>
+        <v>349274</v>
       </c>
       <c r="R4" t="n">
-        <v>6538083</v>
+        <v>6538144</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1047,7 +1032,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk mark.</t>
+          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk till frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,12 +1053,7 @@
         <v>115259670</v>
       </c>
       <c r="B5" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,15 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115263542</v>
+        <v>115262749</v>
       </c>
       <c r="B6" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,13 +1222,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>349167</v>
+        <v>349279</v>
       </c>
       <c r="R6" t="n">
-        <v>6538213</v>
+        <v>6538083</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1307,7 +1282,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk och frisk-fuktig mark precis nedanför en bergsbrant.</t>
+          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk mark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,12 +1303,7 @@
         <v>115263448</v>
       </c>
       <c r="B7" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1455,15 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115259071</v>
+        <v>115263542</v>
       </c>
       <c r="B8" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,13 +1472,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>349246</v>
+        <v>349167</v>
       </c>
       <c r="R8" t="n">
-        <v>6538084</v>
+        <v>6538213</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1567,7 +1532,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Vid fyndplatsen rinner en mindre bäck och inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk till frisk-fuktig mark.</t>
+          <t>Grandominerad något äldre skog med inslag av björk och tall. Relativt stor dimensionsspridning med både smala och grova träd. Bitvis flerskiktad skog. Förekomst av träd med socklar. Enstaka förekomst av liggande, lutande och stående död ved. Småkuperad mark med förekomst av mossklädda block och klippor. Glest fältskikt och nästan heltäckande bottenskikt med olika mossor. Inom skogsbeståndet finns flertalet partier med blötare markförhållanden och vattensamlingar. Fyndplatsen finns på frisk och frisk-fuktig mark precis nedanför en bergsbrant.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 5095-2024 artfynd.xlsx
+++ b/artfynd/A 5095-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115258601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115262749</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115263448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,8 +1582,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115263542</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>